--- a/docentes/Molina Quezada Raúl - Estadisticos 20211.xlsx
+++ b/docentes/Molina Quezada Raúl - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -82,106 +82,34 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>MARCIAL</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>ANASTACIO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
+    <t>NUBE</t>
+  </si>
+  <si>
+    <t>MENDIZABAL</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>CARAZA</t>
-  </si>
-  <si>
-    <t>XOCUA</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>APARICIO</t>
+    <t>ALEMAN</t>
   </si>
   <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>IVAN DE JESUS</t>
-  </si>
-  <si>
-    <t>CONSTANZA XIMENA</t>
-  </si>
-  <si>
-    <t>HIRAM FABIAN</t>
-  </si>
-  <si>
-    <t>CINTHIA</t>
-  </si>
-  <si>
-    <t>EMELIN JIROMI</t>
-  </si>
-  <si>
-    <t>YAZMIN</t>
-  </si>
-  <si>
-    <t>KIMBERLY</t>
+    <t>CHRISTIAN YAIR</t>
+  </si>
+  <si>
+    <t>ALDER ALBERTO</t>
+  </si>
+  <si>
+    <t>ROSA ISELA</t>
   </si>
   <si>
     <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>KAREN ESTEPHANY</t>
-  </si>
-  <si>
-    <t>JARED URIEL</t>
-  </si>
-  <si>
-    <t>LAURA IVETTE</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
   </si>
 </sst>
 </file>
@@ -582,19 +510,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>62.5</v>
+        <v>84.38</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -608,19 +536,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>77.14</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -634,16 +562,16 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>71.43000000000001</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H4">
         <v>10</v>
@@ -660,16 +588,16 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>82.86</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H5">
         <v>10</v>
@@ -725,16 +653,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H2">
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -748,16 +679,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>82.86</v>
+      </c>
+      <c r="H3">
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -771,16 +705,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="E4">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>62.86</v>
+      </c>
+      <c r="H4">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -794,16 +731,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="E5">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>74.29000000000001</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -856,19 +796,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>62.5</v>
+        <v>84.38</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -882,19 +822,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>77.14</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -908,19 +848,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="G4">
-        <v>71.43000000000001</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -934,19 +874,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>82.86</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>9.9</v>
       </c>
     </row>
   </sheetData>
@@ -956,7 +896,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -988,62 +928,59 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920136</v>
+        <v>20330051920100</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920151</v>
+        <v>20330051920099</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" t="s">
-        <v>34</v>
-      </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920042</v>
+        <v>20330051920107</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1052,211 +989,30 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920163</v>
+        <v>20330051920113</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920123</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920129</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920153</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920113</v>
-      </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920283</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920390</v>
-      </c>
-      <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920316</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>19330051920162</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Molina Quezada Raúl - Estadisticos 20211.xlsx
+++ b/docentes/Molina Quezada Raúl - Estadisticos 20211.xlsx
@@ -705,16 +705,16 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>62.86</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H4">
         <v>10</v>
@@ -731,16 +731,16 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G5">
-        <v>74.29000000000001</v>
+        <v>77.14</v>
       </c>
       <c r="H5">
         <v>10</v>
@@ -860,7 +860,7 @@
         <v>88.56999999999999</v>
       </c>
       <c r="H4">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -886,7 +886,7 @@
         <v>88.56999999999999</v>
       </c>
       <c r="H5">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Molina Quezada Raúl - Estadisticos 20211.xlsx
+++ b/docentes/Molina Quezada Raúl - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="29">
   <si>
     <t>Mat</t>
   </si>
@@ -85,9 +85,6 @@
     <t>NUBE</t>
   </si>
   <si>
-    <t>MENDIZABAL</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
@@ -101,9 +98,6 @@
   </si>
   <si>
     <t>CHRISTIAN YAIR</t>
-  </si>
-  <si>
-    <t>ALDER ALBERTO</t>
   </si>
   <si>
     <t>ROSA ISELA</t>
@@ -510,16 +504,16 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>84.38</v>
+        <v>90.63</v>
       </c>
       <c r="H2">
         <v>9.800000000000001</v>
@@ -562,16 +556,16 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>88.56999999999999</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H4">
         <v>10</v>
@@ -653,16 +647,16 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>75</v>
+        <v>84.38</v>
       </c>
       <c r="H2">
         <v>9.800000000000001</v>
@@ -705,16 +699,16 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>71.43000000000001</v>
+        <v>80</v>
       </c>
       <c r="H4">
         <v>10</v>
@@ -796,19 +790,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>84.38</v>
+        <v>90.63</v>
       </c>
       <c r="H2">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -848,16 +842,16 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>88.56999999999999</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H4">
         <v>9.800000000000001</v>
@@ -896,7 +890,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -934,10 +928,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -951,13 +945,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920099</v>
+        <v>20330051920107</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -971,16 +968,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920107</v>
+        <v>20330051920113</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -989,29 +986,6 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920113</v>
-      </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Molina Quezada Raúl - Estadisticos 20211.xlsx
+++ b/docentes/Molina Quezada Raúl - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="27">
   <si>
     <t>Mat</t>
   </si>
@@ -82,28 +82,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>NUBE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>ALEMAN</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>CHRISTIAN YAIR</t>
-  </si>
-  <si>
-    <t>ROSA ISELA</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>RICO</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>FRANCISCO EMMANUEL</t>
+  </si>
+  <si>
+    <t>KAROL</t>
   </si>
 </sst>
 </file>
@@ -504,19 +498,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>90.63</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -530,19 +524,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G3">
-        <v>94.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -556,19 +550,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G4">
-        <v>91.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -582,19 +576,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G5">
-        <v>88.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>9.5</v>
       </c>
     </row>
   </sheetData>
@@ -647,19 +641,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>84.38</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -673,19 +667,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>82.86</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H3">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -699,19 +693,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G4">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -725,19 +719,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>77.14</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>9.5</v>
       </c>
     </row>
   </sheetData>
@@ -790,19 +784,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>90.63</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>9.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -816,19 +810,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>94.29000000000001</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="H3">
-        <v>9.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -842,19 +836,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G4">
-        <v>91.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -868,10 +862,10 @@
         <v>35</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
         <v>4</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
       </c>
       <c r="F5">
         <v>31</v>
@@ -880,7 +874,7 @@
         <v>88.56999999999999</v>
       </c>
       <c r="H5">
-        <v>9.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -890,7 +884,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -922,22 +916,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920100</v>
+        <v>19330051920155</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -945,48 +939,25 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920107</v>
+        <v>19330051920181</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920113</v>
-      </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Molina Quezada Raúl - Estadisticos 20211.xlsx
+++ b/docentes/Molina Quezada Raúl - Estadisticos 20211.xlsx
@@ -813,13 +813,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G3">
-        <v>91.43000000000001</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="H3">
         <v>8</v>
